--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260709.xlsx
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>13,525,655</t>
+          <t>29,263,616</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>29,263,616</t>
+          <t>13,525,655</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
